--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555318021</v>
+        <v>46157.93112441472</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112441472</v>
+        <v>46157.93136341464</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93136341464</v>
+        <v>46157.93383881866</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93383881866</v>
+        <v>46157.93695622567</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93695622567</v>
+        <v>46158.28204838757</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28204838757</v>
+        <v>46158.29652108515</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29652108515</v>
+        <v>46158.29807386538</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29807386538</v>
+        <v>46158.33370301533</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33370301533</v>
+        <v>46158.37221634467</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221634467</v>
+        <v>46158.37275478884</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
